--- a/PTBR/Lang/PTBR/Game/HomeResource.xlsx
+++ b/PTBR/Lang/PTBR/Game/HomeResource.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fogo Sagrado</t>
+          <t>Lareira</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lugar para armazenar suprimentos</t>
+          <t>储存物资的地方</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Espaço onde os moradores vivem</t>
+          <t>住人生活空间</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(Não implementado)</t>
+          <t>(未实装)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(Não implementado)</t>
+          <t>(未实装)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lugar para cultivar e colher plantações</t>
+          <t>种植作物收获的地方</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Entretenimento</t>
+          <t>Diversão</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(Não implementado)</t>
+          <t>(未实装)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(Não implementado)</t>
+          <t>(未实装)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carma</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
